--- a/public/materiais/planilha-controle-licitacoes-FG.xlsx
+++ b/public/materiais/planilha-controle-licitacoes-FG.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Atenção: validade da proposta, garantia de proposta e garantia contratual são coisas diferentes. A garantia de proposta cobre a fase da licitação; a contratual só é emitida depois da assinatura do contrato, em nova apólice.</t>
   </si>
   <si>
-    <t xml:space="preserve">Precisa cotar uma garantia de proposta ou contratual? Fale com a F&amp;G pelo WhatsApp (15) 99861-8659. Corretora registrada na SUSEP (K7E4NJ), painel com mais de 25 seguradoras.</t>
+    <t xml:space="preserve">Precisa cotar uma garantia de proposta ou contratual? Fale com a F&amp;G pelo WhatsApp (15) 99861-8659. Corretora registrada na SUSEP (registro 242160653), painel com mais de 25 seguradoras.</t>
   </si>
   <si>
     <t xml:space="preserve">Nº</t>
